--- a/output/pdf_financials_xlsx/TOM.xlsx
+++ b/output/pdf_financials_xlsx/TOM.xlsx
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.00555</v>
+        <v>-0.00555</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-0.13297</v>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.00555</v>
+        <v>-0.00555</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-0.13297</v>
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.00555</v>
+        <v>-0.00555</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-0.13297</v>
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.00555</v>
+        <v>-0.00555</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.13297</v>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.00555</v>
+        <v>-0.00555</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.13297</v>
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -5305,34 +5305,34 @@
         <v>0</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.627999</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.075237</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>3.288655</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>3.525303</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>3.614764</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>4.439627</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>4.439627</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>3.498128</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>3.498128</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>3.827093</v>
       </c>
     </row>
     <row r="93">
@@ -6637,19 +6637,19 @@
         </is>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-1.633977</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-1.320922</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.679184</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.156471</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.003887</v>
       </c>
       <c r="K118" s="3" t="n">
         <v>0</v>
@@ -8612,7 +8612,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -9476,7 +9480,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -10710,7 +10718,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -12014,7 +12026,11 @@
           <t>Reserves 17</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -15458,7 +15474,11 @@
           <t>Reserves 13 3,288,655</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -16474,7 +16494,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -28496,7 +28520,11 @@
           <t>Exploration and evaluation expenditure</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -33310,7 +33338,11 @@
           <t>Exploration and evaluation expenditure</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr">
         <is>
           <t>-</t>
@@ -49219,10 +49251,10 @@
         </is>
       </c>
       <c r="F487" s="5" t="n">
-        <v>0.13297</v>
+        <v>-0.13297</v>
       </c>
       <c r="G487" s="5" t="n">
-        <v>0.067381</v>
+        <v>-0.067381</v>
       </c>
       <c r="H487" t="inlineStr">
         <is>
@@ -50780,7 +50812,7 @@
         </is>
       </c>
       <c r="E505" s="5" t="n">
-        <v>0.00555</v>
+        <v>-0.00555</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/TOM.xlsx
+++ b/output/pdf_financials_xlsx/TOM.xlsx
@@ -853,13 +853,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.001513</v>
+        <v>0.00555</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.022616</v>
+        <v>0.13297</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.022616</v>
+        <v>0.067381</v>
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
@@ -888,13 +888,13 @@
         <v>0.067477</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.111747</v>
+        <v>0.983303</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.07918699999999999</v>
+        <v>0.51594</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.122204</v>
+        <v>0.520713</v>
       </c>
     </row>
     <row r="11">
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.001513</v>
+        <v>-0.00555</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.022616</v>
+        <v>-0.13297</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.022616</v>
+        <v>-0.067381</v>
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
@@ -969,13 +969,13 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.002434</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.003434</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.002212</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -1794,13 +1794,13 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.732176</v>
+        <v>-2.73461</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-7.47774</v>
+        <v>-7.481174</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-2.376384</v>
+        <v>-2.378596</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-6.756924</v>
@@ -1896,13 +1896,13 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.732176</v>
+        <v>-2.73461</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-7.448648</v>
+        <v>-7.452082</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-2.349556</v>
+        <v>-2.351768</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-6.729612</v>
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-19911.37961453126</v>
+        <v>-19920.55922371622</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-7720.168232897418</v>
+        <v>-7727.436419793652</v>
       </c>
       <c r="I30" s="1" t="inlineStr">
         <is>
@@ -2147,10 +2147,10 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.075</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.245411</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>1.328172</v>
@@ -2159,19 +2159,19 @@
         <v>3.029431</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>1.043888</v>
+        <v>0.206895</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.010391</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.481144</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.708742</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.117209</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>0.25011</v>
@@ -2253,10 +2253,10 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.075</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.245411</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>1.328172</v>
@@ -2265,19 +2265,19 @@
         <v>3.029431</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>1.043888</v>
+        <v>0.206895</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.010391</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.481144</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.708742</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.117209</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>0.25011</v>
@@ -2904,16 +2904,16 @@
         <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.010391</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.481144</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.708742</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.117209</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0</v>
@@ -9734,7 +9734,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -13472,7 +13472,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -16664,7 +16664,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -17642,7 +17642,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -18706,7 +18706,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -36218,7 +36218,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -44072,7 +44072,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
@@ -46382,7 +46382,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
@@ -49154,7 +49154,7 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
@@ -50718,7 +50718,7 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E504" s="5" t="n">
